--- a/web/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
+++ b/web/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,18 +101,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -186,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -233,13 +228,10 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -731,7 +723,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -741,12 +733,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -756,12 +748,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -771,7 +763,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -801,7 +793,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -811,12 +803,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -826,12 +818,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -841,7 +833,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1974,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>1 套</t>
+          <t>3 套</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -2002,7 +1994,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>2 套</t>
+          <t>0 套</t>
         </is>
       </c>
     </row>
@@ -2068,9 +2060,9 @@
         <is>
           <t>A号屋 (蓝塘道23号)
 4575呎 (2房)
-(待售)
-暂无价格
-暂无呎价</t>
+(在售)
+招标项目
+-</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -2118,7 +2110,7 @@
 $49,810/呎</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>A号屋 (蓝塘道35号)
 4571呎 (1房)
@@ -2156,9 +2148,9 @@
         <is>
           <t>B号屋 (蓝塘道23号)
 4602呎 (3房)
-(待售)
-暂无价格
-暂无呎价</t>
+(在售)
+招标项目
+-</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">

--- a/web/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
+++ b/web/files/港岛-黄泥涌-蓝塘道23-39号.xlsx
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4575</v>
+        <v>4571</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4602</v>
+        <v>4599</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4575</v>
+        <v>4571</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>301800000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>65967</v>
+        <v>66025</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4602</v>
+        <v>4599</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>333800000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>72534</v>
+        <v>72581</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4575</v>
+        <v>4571</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>305800000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>66842</v>
+        <v>66900</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4602</v>
+        <v>4599</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>338200000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>73490</v>
+        <v>73538</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4575</v>
+        <v>4571</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>328000000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>71694</v>
+        <v>71757</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4602</v>
+        <v>4599</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>250000000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>54324</v>
+        <v>54360</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4575</v>
+        <v>4571</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>447192000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>97747</v>
+        <v>97832</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4602</v>
+        <v>4599</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>447192000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>97173</v>
+        <v>97237</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4575</v>
+        <v>4571</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>227880000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>49810</v>
+        <v>49853</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4602</v>
+        <v>4599</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>230000000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>49978</v>
+        <v>50011</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4602</v>
+        <v>4599</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>333800000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>72534</v>
+        <v>72581</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4575</v>
+        <v>4571</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>338200000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>73923</v>
+        <v>73988</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4602</v>
+        <v>4599</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>303800000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>66015</v>
+        <v>66058</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4575</v>
+        <v>4571</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>288300000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>63016</v>
+        <v>63072</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4602</v>
+        <v>4599</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>339800000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>73837</v>
+        <v>73886</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       <c r="B6" s="16" t="inlineStr">
         <is>
           <t>A号屋 (蓝塘道23号)
-4575呎 (2房)
+4571呎 (2房)
 (在售)
 招标项目
 -</t>
@@ -2068,46 +2068,46 @@
       <c r="C6" s="17" t="inlineStr">
         <is>
           <t>A号屋 (蓝塘道25号)
-4575呎 (4+房)
+4571呎 (4+房)
 (16年-12月-15日)
 $3.02亿
-$65,967/呎</t>
+$66,025/呎</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
           <t>A号屋 (蓝塘道27号)
-4575呎 (4+房)
+4571呎 (4+房)
 (18年-06月-12日)
 $3.06亿
-$66,842/呎</t>
+$66,900/呎</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
           <t>A号屋 (蓝塘道29号)
-4575呎 (4+房)
+4571呎 (4+房)
 (18年-04月-19日)
 $3.28亿
-$71,694/呎</t>
+$71,757/呎</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
           <t>A号屋 (蓝塘道31号)
-4575呎 (1房)
+4571呎 (1房)
 (26年-01月-01日)
 $4.47亿
-$97,747/呎</t>
+$97,832/呎</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
           <t>A号屋 (蓝塘道33号)
-4575呎 (4+房)
+4571呎 (4+房)
 (25年-12月-22日)
 $2.28亿
-$49,810/呎</t>
+$49,853/呎</t>
         </is>
       </c>
       <c r="H6" s="16" t="inlineStr">
@@ -2122,19 +2122,19 @@
       <c r="I6" s="17" t="inlineStr">
         <is>
           <t>A号屋 (蓝塘道37号)
-4575呎 (4+房)
+4571呎 (4+房)
 (19年-03月-20日)
 $3.38亿
-$73,923/呎</t>
+$73,988/呎</t>
         </is>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
           <t>A号屋 (蓝塘道39号)
-4575呎 (4+房)
+4571呎 (4+房)
 (16年-10月-18日)
 $2.88亿
-$63,016/呎</t>
+$63,072/呎</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       <c r="B7" s="16" t="inlineStr">
         <is>
           <t>B号屋 (蓝塘道23号)
-4602呎 (3房)
+4599呎 (3房)
 (在售)
 招标项目
 -</t>
@@ -2156,73 +2156,73 @@
       <c r="C7" s="17" t="inlineStr">
         <is>
           <t>B号屋 (蓝塘道25号)
-4602呎 (4+房)
+4599呎 (4+房)
 (19年-05月-14日)
 $3.34亿
-$72,534/呎</t>
+$72,581/呎</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
           <t>B号屋 (蓝塘道27号)
-4602呎 (4+房)
+4599呎 (4+房)
 (18年-04月-12日)
 $3.38亿
-$73,490/呎</t>
+$73,538/呎</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
           <t>B号屋 (蓝塘道29号)
-4602呎 (4+房)
+4599呎 (4+房)
 (24年-06月-05日)
 $2.50亿
-$54,324/呎</t>
+$54,360/呎</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
           <t>B号屋 (蓝塘道31号)
-4602呎 (1房)
+4599呎 (1房)
 (26年-01月-01日)
 $4.47亿
-$97,173/呎</t>
+$97,237/呎</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
           <t>B号屋 (蓝塘道33号)
-4602呎 (4+房)
+4599呎 (4+房)
 (24年-02月-09日)
 $2.30亿
-$49,978/呎</t>
+$50,011/呎</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
           <t>B号屋 (蓝塘道35号)
-4602呎 (4+房)
+4599呎 (4+房)
 (19年-05月-14日)
 $3.34亿
-$72,534/呎</t>
+$72,581/呎</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
           <t>B号屋 (蓝塘道37号)
-4602呎 (4+房)
+4599呎 (4+房)
 (18年-02月-27日)
 $3.04亿
-$66,015/呎</t>
+$66,058/呎</t>
         </is>
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
           <t>B号屋 (蓝塘道39号)
-4602呎 (3房)
+4599呎 (3房)
 (21年-07月-26日)
 $3.40亿
-$73,837/呎</t>
+$73,886/呎</t>
         </is>
       </c>
     </row>
